--- a/data/questions.xlsx
+++ b/data/questions.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet'!$A$1:$F$141</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +27,21 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +56,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,167 +429,3411 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="90" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>期望答案</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>分类</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>新建会话</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>回复耗时(s)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>错误信息</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>今天天气怎么样？</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>我无法获取实时天气数据，建议查看天气应用。</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>天气</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>12</v>
-      </c>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Search for a flight from Los Angeles to Sydney on {2026-06-25}, 1 adult, maximum 1 stop</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book. The flights matched our input.</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Multi-turn, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>讲个笑话</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>期望包含一个幽默短故事或段子</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>娱乐</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Find me a vacation rental in Sydney, check-in on 6-25 and check-out on 6-28.</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>A list of vacation rentals in a table; each vacation rental has a deep link to book. The hotels matched our input.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Multi-turn, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1+1等于几？</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>数学</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Which of these hotels have swimming pools?</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>A list of vacation rentals which have pool in a table; each vacation rental has a deep link to book. The hotels matched our input.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Multi-turn, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>你是谁？</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>我是AI助手</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>身份</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Help me book a flight from Sydney back to Los Angeles on {2026-06-29}</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book. The flights matched our input.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Multi-turn, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>帮我写一首关于春天的诗</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>期望返回一首与春天相关的短诗</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>创作</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>flight from New York to Chicago this weekend</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book. Displayed flights from New York to Chicago this weekend</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Change_trip_scope, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>change the date to next Monday</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. Displayed flights from New York to Chicago next Monday</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Change_trip_scope, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>change the destination to Sydney</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. Displayed flights from New York to Sydney next Monday</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Change_trip_scope, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>change the departure to tokyo</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. Displayed flights from Tokyo to Sydney next Monday</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Change_trip_scope, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>change the date to next Thurday</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. Displayed flights from Tokyo to Sydney next Thurday</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Change_trip_scope, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>hotels near New York tomorrow</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. Displayed hotels near New York for tomorrow</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Change_trip_scope, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>London hotel</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. Displayed hotels near London</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Change_trip_scope, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>change the date, check in May 4 and check out May 7</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. Displayed hotels match to the new update date</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Change_trip_scope, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>change the destination to sydney</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. Displayed hotels match to the new destination</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Change_trip_scope, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Subscribe to flights from Los Angeles to Mexico City on {July 4}</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Switch_topic, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>recommend a funny joke movie for me</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Switch topic successfully, and it can load movie-related content successfully.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Switch_topic, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Subscribe to flights from Los Angeles to Mexico City on {July 4}</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Switch_topic, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>what is the weather like today</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Switch topic successfully, and it can load weather-related content successfully.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Switch_topic, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Subscribe to flights from Los Angeles to Mexico City on {July 4}</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Switch_topic, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>recommand a good fast-food restaurant</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Switch topic successfully, and it can load restaurant-related content successfully.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Switch_topic, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Subscribe to flights from Los Angeles to Mexico City on {July 4}</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Switch_topic, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>How is the Sydney Opera House?</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Switch topic successfully, and it can load attractions-related content successfully.</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Switch_topic, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>I’m looking for flights to Rome, Italy, from Chicago, departing in early June 2026.</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book. The flights matched our input.</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>I need to depart on {June 10, 2026} and return on {June 12, 2026}, and I prefer afternoon departures.</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a new list of flights and each flight has a deep link to book. The display sequence is as follows: the flight cards with old dates are displayed at the top, and the flight cards with new dates are displayed at the bottom</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>I need flights to Tokyo, Japan, from London, departing on {September 3, 2026} and returning on {September 10, 2026}</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book. The flights matched our input.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>I need business class</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a new list of flights and each flight has a deep link to book. The display order is as follows: all flight cards are displayed on the top, and designated cabin cards are displayed on the bottom</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Search for flights to Barcelona, Spain, departing from New York on {August 12, 2026} and returning on {August 19, 2026}</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book. The flights matched our input.</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>I want to book United flights for this trip.</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a new list of flights and each flight has a deep link to book. The display sequence is as follows: all flight cards are displayed at the top, and cards of specified airlines are displayed at the bottom</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>I need a hotel in Vancouver, Canada, available in July 2026 (specify some date).</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. The hotels matched our input.</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>I want to check in on {July 10, 2026} and check out on {July 17, 2026}. (different from previous date).</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a new list of hotels and each hotels has a deep link to book. The display order is as follows: the hotel card for the old date is shown on top, and the hotel card for the new date is shown below</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>I’m looking for a hotel in Bangkok, Thailand, available from {June 20, 2026} (check-in) to {June 25, 2026} (check-out).</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. The hotels matched our input.</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>I want to book a hotel that costs under $350 per night.</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a new list of hotels and each hotels has a deep link to book. The display sequence is as follows: all hotel cards are displayed at the top, and filtered hotel cards are displayed at the bottom</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>I need a hotel in Paris, France, available from {June 20, 2026} (check-in) to {June 25, 2026} (check-out).</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. The hotels matched our input.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>I perfer to stay at a 5 star hotel</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a new list of hotels and each hotels has a deep link to book. The display sequence is as follows: all hotel cards are displayed at the top, and filtered hotel cards are displayed at the bottom</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Search for a hotel in Tokyo, Japan, {July 10, 2026} (check-in) to {Jult 15, 2026} (check-out).</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. The hotels matched our input.</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>I want to book a Marriott hotel that meets these criteria.</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a new list of hotels and each hotels has a deep link to book. The display sequence is as follows: all hotel cards are displayed at the top, and filtered hotel cards are displayed at the bottom</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Search for hotels in Tokyo for {July 2, 2026} - {Jult 7, 2026}.</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels in Tokyo based on the user’s input. The hotel results are displayed without initiating any booking.</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Order, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Search for a round-trip flight from Los Angeles to Tokyo for the same dates, 1 adult, economy class.</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights from Los Angeles to Tokyo for the same travel dates. The flights matched our input, including travel dates, route, and economy class selection.</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Order, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Search for hotels in Tokyo for the same travel dates.</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels in Tokyo again for the same travel dates. The display order shows the flight card on top and the hotelcard below</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Order, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Search for hotels in Barcelona for {June 20, 2026} - {June 26, 2026}.</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels in Barcelona based on the user’s input. The hotels matched our input, including travel dates and destination.</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Order, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Search for a round-trip flight from New York to Amsterdam for the same travel dates, 1 adult, economy class.</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights from New York to Amsterdam for the same travel dates. The flights matched our input, including travel dates, route, and economy class selection. The display order shows the hotel card on top and the flight card below</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Order, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Search for a round-trip flight from Sydney to London on {July 12, 2026} - July 18, 2026}, 1 adult, economy class.</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights from Sydney to London based on the user’s input. The flights matched our input, including travel dates, route, and economy class selection.</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Order, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Search for hotels in Paris for the same travel dates.</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels in Paris for the same travel dates. The hotels matched our input, including travel dates and a destination different from the flight search. The display order shows the flight card on top and the hotelcard below</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Order, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Search for hotels in Paris for {July 5, 2026} – {July 10, 2026}.</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels in Paris and each hotel has a deep link to book.</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Order, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Filter hotels by location near the Eiffel Tower and click on the “book now” link (for one hotel).</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>The hotels matched our input, including travel dates and location near the Eiffel Tower.</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Order, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Search for a round-trip flight from Sydney to Paris for the same dates, 1 adult, nonstop preferred.</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights from Sydney to Paris for the same dates and each flight has a deep link to book. The flights matched our input, including travel dates, route, and nonstop preference. The display order shows the flight card on top and the hotelcard below</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Order, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Search for a round-trip flight from Sydney to Tokyo on {July 10, 2026} - {July 17, 2026}, 1 adult, nonstop preferred</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book. The flights matched our input, including travel dates, route, and nonstop preference.</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Order, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Search for hotels in Tokyo for the same travel dates</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels in Tokyo and each hotel has a deep link to book.</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Order, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>check-in on {July 10, 2026} and check-out on {July 17, 2026}</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>The hotels matched our input, including the same travel dates and destination. The display order shows the hotel card on top and the flight card below</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Order, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>“Notion Create a page with a 20-item checklist and a 10-row table”</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>All blocks created successfully</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Create_Update, Notion, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>“Notion add this paragraph to ‘Team OKRs.This is my Team OKRs’”</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Quantum fails safely with clear 'no edit permission'</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Create_Update, Notion, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>“Update my Notion page ‘Roadmap’ with today’s notes”</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Quantum asks which page to update</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Create_Update, Notion, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>“Update the MCP OAuth status to: Implemented on PC and Mobile; remaining risk is release stability”</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Only the intended block/section is updated</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Create_Update, Notion, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>“Using notion, add a section called ‘Open Questions’ with bullets: OAuth stable? Android parity? SSRB status? to Qira Notion V1”</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Section appended to the correct page</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Create_Update, Notion, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>“Create a Notion page under ‘School’ called ‘Week 4 Study Plan’”</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Page created under correct parent</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Create_Update, Notion, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Quantum, create a Notion page with a study guide for my ML midterm.</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>New Notion page is created. Title and sections match intent.</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Create_Update, Notion, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>“Using Notion and based on my notes, what are the open risks for Notion V1?”</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Quantum summarizes risks accurately</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Ask_Notion, Notion, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>“Search Notion for: SSRB / OAuth / MCP / ‘token storage’ ”</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Query parsing succeeds</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Ask_Notion, Notion, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>“Ask Notion to give a summary what’s in ‘Executive Funding Plan’?”</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Quantum responds stating it cannot find a page "executive funding plan"</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Ask_Notion, Notion, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>“Ask Notion to Summarize my ‘PRD Master Doc’”</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Quantum fetches entire content accurately for the page ‘PRD Master Doc’. The process completes within an acceptable response time.</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Ask_Notion, Notion, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>“Notion find my notes on ‘Mars Colony Budget’”</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Quantum returns a 'no results' message.System suggests alternative keywords, date ranges, or nearby matches.</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Ask_Notion, Notion, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>“Notion Show my open action items due this week”</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Quantum identifies the specific database and applies the correct filters (Open status + Due date).</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Ask_Notion, Notion, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>“Using Notion search what did we decide about the Notion integration?”</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Quantum asks a clarifying question (e.g., asking which specific page or timeframe to look at). UI shows a list of top candidate pages for the user to pick from.</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Ask_Notion, Notion, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>“Notion summarize my page called ‘Qira Roadmap’”</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Quantum successfully finds the page via search.</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Ask_Notion, Notion, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>“Ask Notion: find my meeting notes about Project Quantum”</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Quantum searches via MCP and returns relevant pages/blocks. Clicking a result opens the deep link to the correct Notion page or expands the preview in Qira.</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Ask_Notion, Notion, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>How is big data used in real-world applications according to bing?</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Thinking with Qira icon,provides a brief overview of how big data is used in real-world applications with sources Bing displayed. “Dive deeper” and “Explore images” are visible. Thinking with Qira and Perplexity icon, provides a more detailed explanation consistent with the original query, sources Perplexity displayed. 'Explore Images' and "Dive Deeper" are visible Thinking with Qira and Perplexity icon,provides a more detailed explanation consistent with the original query,sources Perplexity displayed. 'Explore Images' and "Dive Deeper" are visible Thinking with Qira and Perplexity icon, provides a deeper explanation of our input query with sources Perplexity displayed. 'Explore Images' and One Related Question are visible</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>What is big data according to bing.</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>provides an explanation of big data with sources displayed; relevant action buttons (e.g., “Dive deeper”) are visible. returns a response relevant to the red panda query.</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>What does a red panda look like?</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>the UI renders correctly; the original big data response is intact with sources displayed, and the original “Dive deeper” button remains visible and functional.</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Search in web: Show me different types of clouds.</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>provides a brief overview of different types of clouds with sources displayed. shows relevant, non-broken cloud images that present different types of clouds.</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Provide a detailed comparison table between the iPhone 15 Pro and the Samsung Galaxy S23 Ultra according to bing.</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>provides a simple information about the iPhone 15 Pro and the Samsung Galaxy S23 Ultra with sources displayed. User does not see `{"component_type":...}` or raw Markdown blocks. JSON is correctly parsed into visual UI components.</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>“What is the capital of France?”</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>provides a simple information about the capital of France with sources displayed. (Dive deeper / Explore images / Sources / Suggestions) are visible. All CTAs remain visible and clickable. UI state is persistent; no CTA disappearance occurs.</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>“What is the history of the Eiffel Tower acccording to bing?”</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Query is accepted and the UI moves to the loading state. No `undefined`, `null`, `NaN`, or template tokens (e.g., `{{placeholder}}`) appear in the UI. All content is correctly rendered as readable text or visual components.</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>“What is the capital of Japan?”</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Result returns within SLA, or a clear error message with a "Retry" button is displayed upon timeout.No infinite “Thinking…” hang occurs. Clicking "Retry" resubmits the same query and returns a result or a new error state.</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>How's the weather today?</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>provides a simple description of today's weather with Bing sources and “Dive deeper” is visible. returns a deeper weather explanation using the same topic, with no context loss after switching to Perplexity; the resolved entity and chat context are preserved.</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>What is big data according to bing.</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Respond with an explanation of Big Data with sources displayed. the “Dive deeper” button is visible, but the “Explore images” button is shown also. provides a more detailed explanation of Big Data</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Show me different styles of wedding dresses in web.</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Respond with content relevant to “different styles of wedding dresses.” A clear textual description is returned with sources displayed.The “Explore images” and the “Dive deeper” button remains available. shows relevant images of wedding dress styles.</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>What is the definition of democracy according to bing?</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>provides a simple explanation of the meaning of democracy with sources Bing displayed. Step 2* provides a more detailed explanation of democracy</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Search in web: what is big data?</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Respond with an explanation of Big Data with sources displayed. the “Dive deeper” button is visible, but the “Explore images” button is shown also.</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>How is big data used in real-world applications according to bing?</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Respond with an explanation of the applications of Big Data with sources displayed. the “Dive deeper” button is visible, but the “Explore images” button is shown also. Provides a more detailed explanation of the applications of Big Data .</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Search in web: what does a red panda look like?</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>A clear, on-topic description of red panda is returned with sources displayed and “Explore images” button is visible. shows images of red panda.</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Show me what a sunflower looks like according to web.</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>provides a simple description of a sunflower with sources displayed. “Dive deeper” and “Explore images” are visible.</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>@PPLX What are the major changes for the 2026 World Cup and where will it be held?</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Provides the correct information match with we input. “Explore images” is shown, and suggestion is shown also.</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>@PPLX Show me famous landmarks in New York City.</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>provides a brief description of famous landmarks in New York City with sources displayed. “Dive deeper” and “Explore images” are visible.</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>What is the definition of democracy in web?</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>provides a simple explanation of the meaning of democracy with sources displayed. “Dive deeper” is visible. “Explore images” is shown also.</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Whats the 3latlas about?</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Thinking with Qira icon, provides a simple explanation of our input query with sources Bing displayed. “Dive deeper” and “Explore images” are visible. Thinking with Qira and Perplexity icon, provides a deeper explanation of our input query with sources Perplexity displayed. 'Explore Images' and One Related Question are visible Thinking with Qira and Perplexity icon, load the content scorll to view all, sources Perplexity displayed. 'Explore Images' and One Related Question are visible Thinking with Qira and Perplexity icon, load the content scorll to view all, sources Perplexity displayed. 'Dive Deeper' and One Related Question are visible Thinking with Qira icon, provides a simple explanation of our input query with sources Bing displayed.</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Show me different styles of wedding dresses according to bing.</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>provides a brief overview of different styles of wedding dresses. with sources displayed. shows images representing different wedding dress styles. provides a more detailed explanation of wedding dress styles.</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Show me the Great Wall of China in web.</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>provides a brief description of the Great Wall of China with sources displayed. provides a more detailed explanation related to the Great Wall of China. shows images of the Great Wall of China.</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Show me different types of clouds in web.</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>provides a brief overview of different types of clouds with sources displayed. shows images representing different types of clouds.</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Show me Mount Fuji in winter in web.</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>provides a brief description of Mount Fuji in winter with sources displayed. provides a more detailed explanation related to Mount Fuji’s winter conditions.</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>How is big data used in real-world applications according to web?</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>provides a brief overview of how big data is used in real-world applications with sources displayed. provides a more detailed explanation consistent with the original query.</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>What does a dachshund look like in web?</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>provides a simple description of a dachshund with sources displayed. “Dive deeper” and “Explore images” are visible.</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>What is the definition of democracy in web?</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>provides a simple explanation of the meaning of democracy with sources Bing displayed.</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>PPLX, golden_test_case, origin_ik3pmagent, phone_full_regression</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>@Expedia Book a flight from New York to Tokyo.</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Qira will ask you to provide the date info and a short explanation.</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>@Expedia, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>@Expedia Departing on Jan 10.</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>A list of hotels in a table; each flight has a deep link to book. Expedia website is launched to the right hotel in the Windows PC default web browser</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>@Expedia, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Show me vacation rentals in Paris next week in Le Marais.</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Qira will ask you to provide the date info and a short explanation</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Vrbo, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Check-in date is {9.25} and stay for 2 nights.</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>A list of vacation rentals (non-smoking, high floor) in a table and each vacation rental has a deep link to book</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Vrbo, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Which of these have rooftop views of the Eiffel Tower?</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Refined list filtered to properties with rooftop terrace/Eiffel Tower views</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Vrbo, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>vacation rental Terrass’ appears in the table.</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Expedia site launches to vacation rental Terrass’ booking page in Windows browser and booked successfully</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Vrbo, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Find me a vacation rental in Barcelona next week.</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Qira will ask you to provide the date info and a short explanation.</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Vrbo, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>check-in on {June 5} and check-out on {June 9}.</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>A list of vacation rentals (non-smoking, high floor) in a table and each vacation rental has a deep link to book.</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Vrbo, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>What about ones with a rooftop pool and in the Gothic Quarter, maybe across from the cathedral?</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Refined list filtered to vacation rentals with rooftop pools; vacation rental Colon is shown in the table of results. Sorted by rating.</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Vrbo, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Find me a vacation rental in Barcelona next week.</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Quautum will ask you to provide the date info and a short explanation</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Vrbo, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>check in date is {9.20} and stayed for 3 nights in Barcelona.</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>A list of at list of vacation rentals (non-smoking, high floor) in a table and each vacation rental has a deep link to book. Refined list filtered to vacation rentals with above 5 starts.</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Vrbo, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Search for a flight from Los Angeles to Sydney on {2026-05-25}, 1 adult, maximum 1 stop</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book. The flights matched our input.</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Flight, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Search for a flight from Tokyo to Dubai on {2026-05-28}, 2 adults, economy class needed</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book. The flights matched our input.</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Flight, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Search for a flight from Frankfurt to Toronto on {2026-05-20}, 2 adults, with 1 seated infant aged 8 months</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book. The flights matched our input.</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Flight, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Search for a flight from Paris to New York on {2026-08-03}, 1 adult, with 1 lap infant aged 10 months</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book. The flights matched our input.</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Flight, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Find a flight from Sydney to Tokyo on {2026-06-22}, 1 adult and 1 senior citizen aged 70</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book. The flights matched our input.</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Flight, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Search for a round-trip flight from New York to London on {2026-04-28}, 2 adults, return date {2026-05-02}</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book. The flights matched our input.</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Flight, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Search for a round-trip flight from Los Angeles to Paris on {2026-07-16}, 1 adult</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book. The flights matched our input.</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Flight, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Book a round-trip flight from Hong Kong (HKG) to San Francisco (SFO) on {2026-05-30}, 2 adults</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Qira asks what date would you like to return.</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Flight, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr"/>
+      <c r="F111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>I would like to return on {2026-06-07}</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book. The flights matched our input.</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Flight, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Search for a flight from Sydney to Los Angeles on {2026-07-25}, 1 adult, departure time no later than 18:30</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book. The flights matched our input.</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Flight, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Search for a flight from Paris to Tokyo on {2026-06-22}, 1 adult, departure time no earlier than 14:00</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book. The flights matched our input.</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Flight, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Help me find a flight from the United States to Japan</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Qira will ask you provide a departcity departure date and destination. Qira will ask you provide a departure date. Qira will provide a list of flights and each flight has a deep link to book. The flights matched our input.</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Flight, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr"/>
+      <c r="F115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Search for flights from Sydney to Frankfurt on {2026-10-10},2 adults</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book. The flights matched our input.</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Flight, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Search for flights from New York, USA to London on {2026-12-20}</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of flights and each flight has a deep link to book. The flights matched our input.</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Flight, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr"/>
+      <c r="F117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>I’m looking for a hotel in Seoul, South Korea, available from {May 15, 2026} to {May 19, 2026}, specifying 2 rooms: each room has 2 adults and 1 children.</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. The hotel matched our input.</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Hotel, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Hotel booking in Tokyo Japan from {June 20, 2026} to {June 25, 2026}</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Qira will ask you to providea list of hotels and each hotel has a deep link to book. Qira will provide the hotel matched our input.</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Hotel, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr"/>
+      <c r="F119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Can you recommend a hotel in Toronto, Canada, for my stay from {June 5, 2026} to {June 9, 2026}, sorted by starrating in DESC order?</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. The hotel matched our input.</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Hotel, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Could you help me find a hotel in Lisbon, Portugal, for check-in on {August 8, 2026} and check-out on {August 12, 2026}, sorted by price in ASC order?</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. The hotel matched our input.</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Hotel, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr"/>
+      <c r="F121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Can you recommend a hotel in Berlin, Germany, with a designated area for guests to park their cars for check-in on {July 1, 2026} and check-out on {July 5, 2026}?</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. The hotel matched our input.</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Hotel, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Could you assist me in finding a hotel in Delhi, India, with a air condition for check-in on {September 22, 2026} and check-out on {September 26, 2026}?</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. The hotel matched our input.</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Hotel, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr"/>
+      <c r="F123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>I’d like to book a hotel in Kyoto, Japan, with a large, bubbling tub in the room or on-site for a relaxing soak, with check-in on {July 12, 2026} and check-out on {July 16, 2026}.</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. The hotel matched our input.</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Hotel, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>I’m looking for a hotel in Seoul, South Korea, that offers complimentary wireless internet access throughout the property, available from {April 15, 2026} (check-in) to {April 19, 2026} (check-out).</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. The hotel matched our input.</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Hotel, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Could you help me find a hotel in Lisbon, Portugal, with a pool to relax and swim, for check-in on {March 8, 2026} and check-out on {March 12, 2026}?</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. The hotel matched our input.</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Hotel, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Search vacation rental in Tokyo, Japan</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Qira will ask you to provide check in and check out date. Qira will provide a list of hotels and each hotel has a deep link to book. The hotel matched our input. pop up the window and the vrbo icon is correct not expedia</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Vrbo, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Find a hotel in Roma, Italy with a well-equipped business center and meeting rooms, for a 3-day stay with check-in tomorrow.</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. The hotel matched our input.</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Hotel, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Book hotels in Tokyo {December 20, 2026} to {December 25, 2026} with free cancellation.</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. The hotel matched our input.</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Hotel, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr"/>
+      <c r="F129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Book hotels in Tokyo from November 10, 2026 to November 15, 2026 with smoking.</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. The hotel matched our input.</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Hotel, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Help me look for a hotel with a maximum rating of 4.0 stars in Luxembourg city that allows check-in next Thursday for 3 days.</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. The hotel matched our input.</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Hotel, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr"/>
+      <c r="F131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Find a hotel rated at least 3.5 stars in Athens，Greece where I can check in {12.25},check out {12.29}</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. The hotel matched our input.</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Hotel, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr"/>
+      <c r="F132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Please find me hotels within 2 kilometers of the Sydney Opera House. I will check in tomorrow and stay for two nights.</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Qira will provide a list of hotels and each hotel has a deep link to book. The hotel matched our input.</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Hotel, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr"/>
+      <c r="F133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Book a direct flight from San Antonio to New York tomorrow ,need round-trip flight,prefer John F. Kennedy International Airport</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Qira asks for return date</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Flight, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>I would like to return in 5 days</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Qira identify direct flight preferences and filter to direct flights only.</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Flight, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr"/>
+      <c r="F135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Find me a hotel in Barcelona next week.</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Quantum will ask you to provide the date info and a short explanation.</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Check-in on {July 11, 2026} and check-out on {July 17, 2026}.</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>A list of hotels (non-smoking, high floor) in a table and each hotel has a deep link to book.</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr"/>
+      <c r="F137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>What about ones with a rooftop pool and in the Gothic Quarter, maybe across from the cathedral?</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Refined list filtered to hotels with rooftop pools; Hotel Colon is shown in the table of results. Sorted by rating.</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Find me a hotel in Barcelona next week.</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Quantum will ask you to provide the date info and a short explanation.</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Hotel, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr"/>
+      <c r="F139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>check in on {April 29, 2026} and check out on {May 6, 2026}.</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>A list of hotels (non-smoking, high floor) in a table; each hotel has a deep link to book. Refined list filtered to hotels with rooftop pools; Hotel Colon is shown in the table of results. Expedia website is launched to the right hotel in the Windows PC default web browser; booked successfully.</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Hotel, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr"/>
+      <c r="F140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Only premium economy flights, and hotels with a gym.</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Refined flight list shows premium economy only; refined hotel list shows gym amenities. Hotel Century Southern Tower is shown. Expedia web site in launched to the right hotel in the Windows PC default web browser. And booked successfully.</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Flight, Hotel, golden_test_case, origin_ik3pmagent</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr"/>
+      <c r="F141" s="2" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>